--- a/Data/Lambayeque/noticias_lambayeque_20261019_20261026.xlsx
+++ b/Data/Lambayeque/noticias_lambayeque_20261019_20261026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,10 +470,103 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Fenómeno El Niño: Tumbes y Piura esperan lluvias de hasta 40 litros por m² hoy lunes 26</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Según el aviso meteorológico N.º 435, en la costa interior de Piura se esperan lluvias de moderada a fuerte intensidad, mientras que en la sierra las precipitaciones serán de ligera a moderada intensidad.
+Estos eventos estarán acompañados de descargas eléctricas y ráfagas de viento cercanas a los 40 kilómetros por hora.
+????? #Aviso #MINAM #SENAMHI El 26 de octubre, continuarán las precipitaciones en la costa norte y sierra.? Estas precipitaciones estarán acompañadas de descargas eléctricas y ráfagas de viento.?? https://t.co/PaMlOv6Igp https://t.co/YofTj5FYWS — Senamhi (@Senamhiperu) October 25, 2026 El organismo, adscrito al Ministerio del Ambiente (Minam), recomendó a la población extremar las precauciones, mantenerse informada sobre la evolución de las condiciones meteorológicas y seguir las indicaciones de las autoridades.
+Lea también: Fenómeno El Niño en Piura: lluvias intensas inundan viviendas y arrastran lodo en Ayabaca ¿Cuánto lloverá este lunes 26 de octubre? El pronóstico del Senamhi establece los siguientes acumulados de precipitación para la jornada: Lea también: El Niño: lluvias se intensificarán desde noviembre y podrían alcanzar los 300 mm al día Costa norte: entre 4 y 40 mm/día, sierra norte: entre 10 y 25 mm/día, sierra centro: entre 8 y 15 mm/día, sierra sur: entre 6 y 24 mm/día.
+Nota de Prensa N.° 348-2026 | El @indeciperu recomienda medidas de preparación ante precipitaciones en la costa norte y sierra.
+Más información ?? https://t.co/SbBcdQSqO6 — COEN - INDECI (@COENPeru) October 26, 2026 En la sierra norte también se prevé la caída de granizo en localidades situadas por encima de los 2,800 metros sobre el nivel del mar.
+Las precipitaciones podrían presentarse junto con tormentas eléctricas y fuertes ráfagas de viento.
+Asimismo, el Senamhi no descarta la presencia de lloviznas en distritos próximos al litoral de la costa centro y sur.
+¿Qué regiones serán afectadas por las lluvias? El aviso meteorológico comprende provincias de 16 departamentos del país, desde la costa norte hasta la sierra sur y la selva alta.
+En el norte, el pronóstico incluye las siguientes provincias: Tumbes: Contralmirante Villar, Tumbes y Zarumilla; Piura: Ayabaca, Huancabamba, Morropón, Paita, Piura, Sullana y Talara; Lambayeque: Ferreñafe y Lambayeque; Cajamarca: Cajabamba, Cajamarca, Celendín, Chota, Cutervo, Hualgayoc, Jaén, San Ignacio, San Marcos, San Miguel, San Pablo y Santa Cruz.
+Asimismo, Amazonas: Chachapoyas y Luya; La Libertad: Bolívar, Gran Chimú, Otuzco, Pataz, Sánchez Carrión y Santiago de Chuco; y San Martín: Mariscal Cáceres y Tocache.
+En la zona centro del país, las precipitaciones alcanzarán provincias de Áncash, Huánuco, Junín, Pasco y Huancavelica.
+En el sur, el pronóstico comprende provincias de Apurímac, Ayacucho, Cusco y Puno, donde se esperan precipitaciones de acuerdo con los rangos previstos para la sierra.
+Senamhi recomienda extremar precauciones Ante la previsión de precipitaciones y fenómenos meteorológicos de considerable magnitud, el Senamhi exhortó a la población a mantenerse atenta a las actualizaciones del pronóstico y cumplir las recomendaciones de las autoridades.
+Las lluvias acompañadas de descargas eléctricas, granizo y ráfagas de viento pueden generar condiciones peligrosas, por lo que se recomienda evitar la exposición durante las tormentas y mantenerse informados a través de los canales oficiales.
+Más en Andina: ????? Las intensas lluvias del domingo 25 de octubre inundaron viviendas y arrastraron lodo por calles de Ayabaca, en la sierra de Piura.
+También se reportaron pequeños deslizamientos.
+Las familias esperan la evaluación de daños y medidas de prevención.
+?? https://t.co/7Jl4S9tBTc https://t.co/6g7FDovKi9 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 26, 2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-fenomeno-nino-tumbes-y-piura-esperan-lluvias-hasta-40-litros-m²-hoy-lunes-26-1097363.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Kit para el diagnóstico molecular de 18 virus respiratorios hecho en Perú triunfa en Corea</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Esta tecnología hecha en el Perú obtuvo una medalla de oro en la 19ª Exposición Internacional de Inventos de Mujeres en Corea del Sur (KIWIE 2026 ).
+En entrevista con la agencia Andina , la coordinadora técnica del proyecto, Nancy Rojas Serrano, explica que este kit nació tras la pandemia de Covid-19, cuando se evidenció la escasez de reactivos, materiales e insumos para el diagnóstico.
+Fue en ese momento que los investigadores del INS decidieron desarrollar un kit de diagnóstico molecular para virus respiratorios, para lograrlo postularon a un financiamiento de Concytec y ganaron.
+El proyecto empezó en el 2022 y acaba de concluir con buenos resultados en el 2025.
+Lee también: Inventora peruana crea un innovador espéculo ginecológico y gana concurso en Corea “Este kit utiliza tecnología de PCR multiplex en tiempo real y es capaz de detectar los virus respiratorios más comunes que afectan a la población peruana, incluyendo el virus de la influenza, el virus sincitial respiratorio, SARS-Cov-2, adenovirus, entre otros”, detalla la bióloga Nancy Rojas.
+Características del kit La investigadora agrega que está compuesto de cinco paneles, superando significativamente el alcance de los kits comerciales convencionales en el país, los cuales solo detectan 4 virus.
+"A diferencia de las opciones comerciales estandarizadas en el mercado peruano que solo cubren 4 agentes patógenos (Influenza A, Influenza B, Virus Sincitial Respiratorio y SARS-CoV-2), nuestro kit integra en una sola plataforma la detección de 18 virus", enfatiza.
+Además, el Kit ‘Kuskalla Samasunchik’ está diseñado para 96 determinaciones, es decir permite la evaluación de hasta 96 pacientes por kit , explica Rojas.
+" Incluye 5 paneles respiratorios moleculares , control positivo, control negativo, la enzima transcriptasa reversa (RT) y controles internos.
+Un paciente puede obtener su resultado en un tiempo estimado de 3 horas utilizando extracción manual, pero con sistemas automatizados el tiempo total de diagnóstico puede reducirse a 2 horas ", precisa la bióloga peruana, facilitando así la descentralización de las pruebas en las regiones del país.
+Validación exitosa Las primeras pruebas que se realizaron en laboratorio fueron favorables, luego vino la fase de evaluación clínica y en Campo, la cual se realizó en el laboratorio de biología molecular del área de investigación del Hospital Regional de Lambayeque en el 2024.
+Lee también: Peruano desarrolla proyecto en ingeniería de tejido corneal y gana concurso internacional Para ello, explica Rojas, se reclutó a pacientes con cuadros clínicos respiratorios mediante la colaboración multidisciplinaria de médicos neumólogos, pediatras, geriatras y ginecólogos.
+El desempeño favorable ante la evaluación con muestras clínicas en entorno real, superó las exigencias técnicas requeridas por Concytec para el cierre del proyecto.
+Durante este tiempo se consolidó la documentación técnica necesaria para la transferencia estandarizada de tecnología entre centros de producción e investigación.
+Como bien lo explica, la bióloga Rojas, entre julio y agosto de 2025, el Centro Nacional de Productos Biológicos produjo un lote adicional para la consolidación de informes técnicos internos.
+Hacia finales del mismo año, se programó la producción de un segundo lote destinado tanto al soporte de proyectos internos de investigación del INS como a la recopilación de requisitos regulatorios.
+Actualmente, se viene gestionando el registro sanitario en Digemid del kit y se encuentra en proceso una solicitud de patente de invención ante Indecopi.
+Triunfo en Corea del Sur Precisamente fue a través de Indecopi que este dispositivo participó en la competencia de inventoras KIWIE 2026 y logró se reconocida con una medalla de oro para nuestro país.
+Otras dos tecnologías desarrolladas por el INS también fueron premiadas se trata de: Control de Calidad de Fármacos – Kit "Hampi Tariki": diseñado para pruebas rápidas de evaluación sanitaria de medicamentos, asegurando tratamientos seguros y eficaces en todo el país.
+Sistema de Filtración de Arsénico: purifica agua contaminada en zonas vulnerables durante emergencias como el Fenómeno El Niño (FEN), previniendo enfermedades graves.
+Con estos triunfos, el Instituto Nacional de Salud reafirma su compromiso de seguir impulsando la investigación científica, el talento de sus profesionales y la protección de invenciones con alto impacto social para resguardar la vida y la salud de todos los peruanos.
+El evento se llevó a cabo del 16 al 18 de julio en la República de Corea, y reunió a 452 invenciones provenientes de 19 países, en donde el Perú logró destacar nuevamente como la delegación con mayor número de inventos participantes, esta vez al concentrar el 67.7 % del total de proyectos inscritos.
+La representación nacional estuvo conformada por 20 universidades, 1 instituto de investigación, 1 instituto de formación industrial y 2 empresas, que en conjunto obtuvieron 306 medallas.
+Revisa más noticias sobre ciencia, tecnología e innovación en la Agencia Andina y escucha historias inspiradoras en Andina Podcast.
+Más en Andina: ???? ¡Descarga en Google Play la renovada app de Andina! https://t.co/tsQ0Psvp80 ?? Integra videos, podcasts informativos y otros contenidos multimedia ??? Funciones extra: lectura en voz alta, búsqueda por voz, modo oscuro y más.
+¡Ya disponible! pic.twitter.com/lgWCtjpdSk (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) January 26, 2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-kit-para-diagnostico-molecular-18-virus-respiratorios-hecho-peru-triunfa-corea-1097331.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>El Niño: Indecopi orienta a pasajeros de transporte terrestre sobre principales derechos</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Destacó la importancia de verificar el estado de las vías y contratar empresas autorizadas.
 Durante la jornada, se difundió la Guía para consumidores en situaciones de emergencia , una herramienta informativa que reúne los derechos de los pasajeros y recomendaciones para tomar decisiones de consumo informadas.
@@ -485,112 +578,77 @@
 Más en Andina: Casi 4 de cada 10 trabajadores en Perú sienten que 2026 ha sido mejor de lo esperado ?? https://t.co/Oz5He2LYPH https://t.co/m9AwfjaFti (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 25, 2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-el-nino-indecopi-orienta-a-pasajeros-transporte-terrestre-sobre-principales-derechos-1097319.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Arequipa: prevén que a fin de mes culmine descolmatación de torrenteras</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>“Esperemos terminar a finales de mes, preparándonos para la posible entrada de agua en Arequipa por el Fenómeno El Niño en Arequipa”, recalcó el representante del Poder Ejecutivo, en declaraciones a TV Perú.
-[Lea también: Décimo tercer friaje en la selva provocará desde hoy lluvias y descenso de temperatura ] Arnillas se encuentra en Arequipa, inspeccionando los trabajos de descolmatación en la torrentera El Chullo , que cruza tres distritos de la provincia de Arequipa.
-Este desfogue de aguas se bloqueó el año pasado, derivando ello en un desborde que inundó diversas avenidas de la Ciudad Blanca.
-“Tenemos tiempo para limpiar la caja hidráulica y descolmatar para que transite la cantidad de agua que venga, pero no para hacer muros de contención y ampliar la caja hidráulica en zonas en las que la han reducido a dos metros cuando debería tener 14”, precisó el ministro.
-24 puntos para descolmatar En total, se encuentran en esta jurisdicción 24 puntos que están siendo atendidos de esta forma, dijo el ministro.
-De ellos, 4 están en la citada torrentera, extendiéndose a lo largo de 4.7 kilómetros, precisó.
-“Hoy estamos en el tercer punto, que ya está limpio, y se seguirá descolmatando esta torrentera”, informó Arnillas.
-[Lea también: ¿Qué días serán no laborables en Lambayeque y Cajamarca? ] En ese contexto, recomendó a la población no arrojar basura o desmonte a las torrenteras.
-“Son como las venas del cuerpo: siempre va a na pasar agua por ellas, y como ciudadanos tenemos que tomar conciencia de que no son basurero”, expresó.
-Maquinaria y presupuesto Para la ejecución de estos trabajos, el Ministerio de Vivienda, Construcción y Saneamiento ha dispuesto tres equipos de maquinaria.
-Además, ha contratado a 13 pools de este tipo más, refirió el ministro.
-“Estamos trabajado al 100%, incluso en dos turnos” , manifestó.
-Este sector ha recibido una asignación presupuestal de 25 millones de soles para atender labores de esta índole en 55 puntos en todo el país , añadió Arnillas.
-[Lea también: Gobierno prorroga estado de emergencia en distritos de Madre de Dios y de Cajamarca ] Por otro lado, el ministro destacó la declaración en emergencia de los sectores de Vivienda, Urbanismo y Desarrollo Urbano y Saneamiento en la cartera ministerial que él encabeza.
-Ello se oficializó hoy mediante el decreto supremo 016-2026-VIVIENDA , que aparece en la separata de normas legales del Diario El Peruano.
-“Hemos declarado esa emergencia porque cuando entramos al gobierno encontramos 1.9 millones de déficit de vivienda a nivel nacional.
-15 millones de peruanos que no tienen servicio de desagüe y 9 millones que no tienen servicio de agua potable domiciliaria de calidad”, explicó, Esta declaratoria permitirá “reorganizar profundamente” los ámbitos mencionados, consideró.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-arequipa-preven-a-fin-mes-culmine-descolmatacion-torrenteras-1097282.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visita del papa León XIV: ¿qué días serán no laborables en Lambayeque y Cajamarca?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>En la medida dispuesta por el Poder Ejecutivo, vía el decreto supremo Nº 020-2026-TR , se declara días no laborables, sujetos a compensación, por la visita del Sumo Pontífice de la Iglesia Católica.
-[Lea también: Chiclayo espera con fe y gran expectativa la visita del papa León XIV ] La medida alcanza a los trabajadores del sector público y privado , de acuerdo con las fechas establecidas para cada ámbito geográfico.
-En el caso de Lambayeque el Gobierno declaró el viernes 13 y sábado 14 de noviembre de 2026 como días no laborables compensables para los trabajadores públicos y privados, debido a las actividades previstas por la visita del papa León XIV a Chiclayo y a la provincia cajamarquina de Santa Cruz.
-La medida se aplica también para las regiones de Cajamarca, La Libertad y Piura , para favorecer la movilización de los devotos y turistas.
-Lea también: Chiclayo quiere convertir visita del Papa en una experiencia religiosa y turística única Al alcanzar estos días no laborables tanto al sector público como al privado, se busca facilitar la participación de los ciudadanos en las actividades vinculadas con la visita del sumo pontífice , prevista del 11 al 16 de noviembre de este año.
-¿Qué días no se trabajará en estas regiones? Viernes 13 de noviembre: Día no laborable compensable para trabajadores de los sectores público y privado de Lambayeque, Cajamarca, La Libertad y Piura.
-Sábado 14 de noviembre: Segundo día no laborable compensable en las cuatr regiones.
-¿Son feriados o días no laborables? Es importante precisar que no son feriados nacionales, sino días no laborables sujetos a compensación.
-Esto significa que las horas dejadas de trabajar deberán recuperarse posteriormente, según las disposiciones establecidas en el decreto.
-- Sector público: las horas no trabajadas deberán compensarse dentro de los diez días inmediatos posteriores o en la oportunidad que establezca el titular de cada entidad.
-[Lea también: Visita del papa León XIV: 100,000 devotos asistirán a misa que se celebrará en Santa Cruz ] - Sector privado: el empleador y los trabajadores deberán acordar cómo se recuperarán las horas.
-Si no existe acuerdo, el empleador determinará la forma de compensación.
-- Servicios esenciales: las entidades públicas y empresas privadas comprendidas en las actividades indispensables deberán adoptar medidas para garantizar la continuidad de los servicios a la población.
-¿Qué otras regiones tendrán días no laborables? El decreto también establece disposiciones especiales para Lima, la Provincia Constitucional del Callao, Cusco y Ucayali.
-En Lima y el Callao, los días no laborables serán el 11 y 12 de noviembre, desde la 1:00 p.
-m.
-hasta la medianoche, y el 16 de noviembre durante toda la jornada.
-En Cusco y Ucayali, el 15 de noviembre será día no laborable únicamente para el sector privado.
-Por último, la disposición precisa que se busca facilitar la participación ciudadana y contribuir a la organización de las actividades previstas durante la visita papal.
-Más en Andina: El Gobierno prorrogó por 60 días, a partir del 28 de octubre, el estado de emergencia en los distritos de Tambopata, Inambari, Las Piedras y Laberinto, de la provincia de Tambopata, y en los distritos de Madre de Dios y Huepetuhe, de la provincia de Manu, en Madre de Dios.?? https://t.co/2iAHhacRpS (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 25, 2026</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-visita-del-papa-leon-xiv-dias-seran-no-laborables-lambayeque-y-cajamarca-1097062.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Resultados ONPE en región Lambayeque al 99.916 %: revisa aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios iniciaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación en región Lambayeque según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/resultados-en-lambayeque-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Papa León XIV en Perú: museos de Lambayeque atenderán hasta las 8 p.m. en noviembre</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>El Ministerio de Cultura ampliará de manera extraordinaria el horario de atención de tres museos de la región Lambayeque del 1 al 15 de noviembre, como parte de la ruta “Los Caminos del Papa León XIV” y en el marco de la próxima visita del pontífice a la región. La medida comprende el Museo Arqueológico Nacional Brüning, el Museo Tumbas Reales de Sipán y el Museo Nacional de Sicán, que atenderán de lunes a domingo, de 9 a.m. a 8 p.m. La ampliación busca facilitar el acceso de los visitantes a las colecciones y al patrimonio arqueológico que conservan estos espacios culturales. Carlos Wester La Torre, director de la Unidad Ejecutora 005 Naylamp Lambayeque del Ministerio de Cultura, señaló que el nuevo horario permitirá incorporar los museos en los recorridos turísticos por la región, junto con los destinos vinculados a la labor pastoral que desarrolló León XIV cuando fue obispo de Chiclayo. “Esta medida contribuye a la acogida de los visitantes nacionales y extranjeros que llegarán a Lambayeque, y facilita la organización de itinerarios que integren los atractivos religiosos con los museos de la región, donde se conserva y difunde el legado de las antiguas sociedades prehispánicas”, manifestó Wester La Torre. El funcionario también informó que los días 13 y 14 de noviembre los seis museos de Lambayeque preparan una jornada cultural especial, que incluirá actividades, activaciones y espectáculos artísticos dirigidos a las familias, en el marco de la visita del papa León XIV a la región. Sin embargo, la ampliación extraordinaria del horario se aplicará únicamente a los tres museos mencionados. El Museo de Sitio Túcume, el Museo de Sitio Huaca Rajada-Sipán y el Museo de Sitio Huaca Chotuna-Chornancap mantendrán sus horarios habituales de atención. A través de la Unidad Ejecutora 005 Naylamp Lambayeque, el Ministerio de Cultura invitó a la ciudadanía a visitar estos espacios y conocer el patrimonio cultural de la región.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/peru/lambayeque/papa-leon-xiv-en-peru-museos-de-lambayeque-atenderan-hasta-las-8-pm-en-noviembre-apuesplan-ultimas-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>¿Por qué 15 de noviembre será no laborable solo para el sector privado en Cusco y Ucayali?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>A diferencia de otras regiones comprendidas en el Decreto Supremo N.° 020-2026-TR publicado por el Gobierno con motivo de la visita del papa León XIV al Perú, la disposición establece que los trabajadores del sector público de Cusco y Ucayali no están incluidos en este beneficio.
 La medida busca facilitar la participación de la población y trabajadores en las actividades vinculadas con la visita del sumo pontífice, prevista del 11 al 16 de noviembre de 2026.
@@ -612,27 +670,99 @@
 La visita del papa León XIV al Perú constituye un acontecimiento de especial trascendencia espiritual, histórica y social, según los considerandos del decreto, que establece facilidades laborales diferenciadas para las regiones comprendidas en el recorrido del pontífice.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-por-15-noviembre-sera-no-laborable-solo-para-sector-privado-cusco-y-ucayali-1097083.aspx</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Papa León XIV: museos de Lambayeque amplían horario de atención por visita del pontífice</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>La medida comprende el Museo Arqueológico Nacional Brüning, el Museo Tumbas Reales de Sipán y el Museo Nacional de Sicán, que atenderán de lunes a domingo, de 9:00 a 20:00 horas, con el propósito de facilitar el acceso de los visitantes a las colecciones y al patrimonio arqueológico que albergan.
+Carlos Wester La Torre, director de la Unidad Ejecutora 005 Naylamp Lambayeque del Ministerio de Cultura, señaló que la ampliación permitirá a los visitantes incluir estos espacios culturales en sus recorridos por la región, junto con los destinos vinculados a la labor pastoral que desarrolló León XIV cuando fue obispo de Chiclayo.
+“Esta medida contribuye a la acogida de los visitantes nacionales y extranjeros que llegarán a Lambayeque, y facilita la organización de itinerarios que integren los atractivos religiosos con los museos de la región, donde se conserva y difunde el legado de las antiguas sociedades prehispánicas”, manifestó Wester La Torre.
+Asimismo, informó que, los días 13 y 14 de noviembre, en el marco de la visita del papa León XIV a Lambayeque, los seis museos de la región preparan una jornada cultural especial con actividades, activaciones y espectáculos artísticos dirigidos a las familias.
+También, precisó que la ampliación extraordinaria del horario se aplicará exclusivamente a los tres museos antes mencionados, por lo que el Museo de Sitio Túcume, el Museo de Sitio Huaca Rajada-Sipán y el Museo de Sitio Huaca Chotuna-Chornancap atenderán en sus horarios habituales.
+El Ministerio de Cultura, a través de la Unidad Ejecutora 005 Naylamp Lambayeque, invita a la ciudadanía a visitar estos espacios y conocer el patrimonio cultural de la región.
+Más en Andina:</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-papa-leon-xiv-museos-lambayeque-amplian-horario-atencion-visita-del-pontifice-1097346.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Arequipa: prevén que a fin de mes culmine descolmatación de torrenteras</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>“Esperemos terminar a finales de mes, preparándonos para la posible entrada de agua en Arequipa por el Fenómeno El Niño en Arequipa”, recalcó el representante del Poder Ejecutivo, en declaraciones a TV Perú.
+[Lea también: Décimo tercer friaje en la selva provocará desde hoy lluvias y descenso de temperatura ] Arnillas se encuentra en Arequipa, inspeccionando los trabajos de descolmatación en la torrentera El Chullo , que cruza tres distritos de la provincia de Arequipa.
+Este desfogue de aguas se bloqueó el año pasado, derivando ello en un desborde que inundó diversas avenidas de la Ciudad Blanca.
+“Tenemos tiempo para limpiar la caja hidráulica y descolmatar para que transite la cantidad de agua que venga, pero no para hacer muros de contención y ampliar la caja hidráulica en zonas en las que la han reducido a dos metros cuando debería tener 14”, precisó el ministro.
+24 puntos para descolmatar En total, se encuentran en esta jurisdicción 24 puntos que están siendo atendidos de esta forma, dijo el ministro.
+De ellos, 4 están en la citada torrentera, extendiéndose a lo largo de 4.7 kilómetros, precisó.
+“Hoy estamos en el tercer punto, que ya está limpio, y se seguirá descolmatando esta torrentera”, informó Arnillas.
+[Lea también: ¿Qué días serán no laborables en Lambayeque y Cajamarca? ] En ese contexto, recomendó a la población no arrojar basura o desmonte a las torrenteras.
+“Son como las venas del cuerpo: siempre va a na pasar agua por ellas, y como ciudadanos tenemos que tomar conciencia de que no son basurero”, expresó.
+Maquinaria y presupuesto Para la ejecución de estos trabajos, el Ministerio de Vivienda, Construcción y Saneamiento ha dispuesto tres equipos de maquinaria.
+Además, ha contratado a 13 pools de este tipo más, refirió el ministro.
+“Estamos trabajado al 100%, incluso en dos turnos” , manifestó.
+Este sector ha recibido una asignación presupuestal de 25 millones de soles para atender labores de esta índole en 55 puntos en todo el país , añadió Arnillas.
+[Lea también: Gobierno prorroga estado de emergencia en distritos de Madre de Dios y de Cajamarca ] Por otro lado, el ministro destacó la declaración en emergencia de los sectores de Vivienda, Urbanismo y Desarrollo Urbano y Saneamiento en la cartera ministerial que él encabeza.
+Ello se oficializó hoy mediante el decreto supremo 016-2026-VIVIENDA , que aparece en la separata de normas legales del Diario El Peruano.
+“Hemos declarado esa emergencia porque cuando entramos al gobierno encontramos 1.9 millones de déficit de vivienda a nivel nacional.
+15 millones de peruanos que no tienen servicio de desagüe y 9 millones que no tienen servicio de agua potable domiciliaria de calidad”, explicó, Esta declaratoria permitirá “reorganizar profundamente” los ámbitos mencionados, consideró.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-arequipa-preven-a-fin-mes-culmine-descolmatacion-torrenteras-1097282.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Fenómeno El Niño: ¿el incremento de calor implica un mayor riesgo de cáncer de piel?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Frente a este panorama de bochorno y jornadas sofocantes, surge una interrogante recurrente entre la ciudadanía: ¿el incremento de calor implica realmente un mayor riesgo de desarrollar cáncer de piel? Para la doctora Marjorie Huarac Linares , cirujana oncóloga especialista en piel del Instituto Nacional de Enfermedades Neoplásicas (INEN), la respuesta exige marcar una distinción fundamental, ya que las alteraciones en la piel no son ocasionadas directamente por el calor, sino por la acción perjudicial de los rayos de radiación ultravioleta (UV).
 ¿Qué son los rayos UV? El ingeniero José Inoue , especialista de la Subdirección de Evaluación del Ambiente Atmosférico del Senamhi , precisa que la radiación ultravioleta es una porción de energía solar de alta potencia capaz de generar severos perjuicios en la salud, como cataratas oculares, debilitamiento del sistema inmunológico y cáncer de piel.
@@ -660,87 +790,165 @@
 ?? https://t.co/4rLeZqQt70 https://t.co/LUPxbGxJz5 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-fenomeno-nino-incremento-calor-implica-un-mayor-riesgo-cancer-piel-1097097.aspx</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>El Comercio</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Lambayeque: Desagües colapsan por tercer día consecutivo en urbanización de Chiclayo</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Vecinos y comerciantes de la urbanización Santa Victoria, en Chiclayo (Lambayeque) denunciaron el colapso de varios desagües, lo que provocó la acumulación de aguas servidas en el cruce avenidas Libertad y Grau desde hace tres días. Testimonios recogidos por Exitosa Noticias denuncian que la falla genera olores insoportables y pone en riesgo a un centro médico cercano debido al estancamiento de aguas residuales. Frente a esto, los residentes manifestaron su temor por la llegada de las lluvias asociadas al Fenómeno El Niño, ya que el agua empozada podría extenderse hacia otras calles del sector, y multiplicar estos incidentes. Uno de los comerciantes de la zona, José López, sostuvo que el agua sigue acumulada y no hay respuesta de la empresa encargada del servicio. “Que vengan inmediatamente las motobombas sobre el agua”, demandó el trabajador.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://elcomercio.pe/peru/lambayeque/lambayeque-desagues-colapsan-por-tercer-dia-consecutivo-en-urbanizacion-de-chiclayo-fenomeno-el-nino-ultimas-noticia/</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Visita del papa León XIV: Perú ofrece 220,000 plazas-cama en destinos de su recorrido</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MEF señala que están trabajando para que economía crezca sostenidamente en próximos 5 años Según la información del sector, esta capacidad de alojamiento comprende alrededor de 126,000 habitaciones disponibles.
-Además, se suman unas 48,000 habitaciones de alquiler temporal a través de plataformas como Airbnb, que amplían las alternativas para los visitantes nacionales y extranjeros.
-Lima y Callao concentran la mayor oferta, con 167,000 plazas-cama en aproximadamente 9,000 establecimientos de hospedaje.
-Les siguen Cusco, con 28,000 plazas-cama en cerca de 1,100 establecimientos; Chiclayo y localidades cercanas de las provincias de Lambayeque y Ferreñafe, con 15,000 plazas-cama en 569 establecimientos; Pucallpa, con 9,000 plazas-cama; y Santa Cruz de Succhabamba y Chota, en Cajamarca, con 2,000 plazas-cama.
-Las cifras corresponden a junio de 2026 y dan cuenta de la capacidad de alojamiento registrada en los ámbitos considerados para la visita papal.
-Impacto en la economía El Mincetur proyecta que la visita del papa León XIV podría atraer a más de 854,000 visitantes a los destinos incluidos en su itinerario y generar un impacto económico directo estimado en 308,4 millones de soles.
-La llegada de viajeros representa una oportunidad para dinamizar las economías locales mediante una mayor demanda de servicios turísticos, entre ellos hospedaje, alimentación, transporte y comercio, con efectos en los ingresos de emprendedores y trabajadores de las localidades anfitrionas.
-A nivel nacional, el Perú registró 28,722 establecimientos de hospedaje en 2025, de acuerdo con el informe anual del Mincetur.
-Esta cifra representó un crecimiento de 2,4% respecto al año anterior y superó en 20,1% los niveles prepandemia, según el sector.
-Más en Andina: ?? Las ventas de vehículos livianos nuevos alcanzaron un pico histórico entre enero y agosto del 2026, al sumar 167,244 unidades comercializadas, cifra que representa un crecimiento de 39.5%.
-https://t.co/CnOVIriRwF pic.twitter.com/umjYiIKhwh (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) September 18, 2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-visita-del-papa-leon-xiv-peru-ofrece-220000-plazascama-destinos-su-recorrido-1097155.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Calor extremo en Lambayeque: región registra temperaturas de 35.2 °C en últimas 24 horas</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>El informe, que comprende el periodo desde las 7:00 a.
+m.
+del jueves 22 hasta las 7:00 a.
+m.
+del viernes 23 de octubre, revela que las localidades de la costa lambayecana continúan registrando temperaturas elevadas , mientras que en las zonas altoandinas se presentan condiciones más frías, como en Incahuasi, donde la temperatura mínima descendió a 10.4 °C.
+Motupe y Cayaltí encabezaron los registros de temperatura máxima , con 35.2 °C cada una , seguidas de Jayanca, con 35 °C; Sipán y Vista Florida, en Chiclayo, con 34.9 °C; y Oyotún, con 33.6 °C.
+En Pasabar, distrito de Olmos, se reportaron 33.4 °C.
+Otros registros fueron 33.2 °C en Lambayeque, 32.7 °C en el aeropuerto de Chiclayo, 32.6 °C en Tongorrape y Tinajones, y 30.6 °C en Reque.
+Incahuasi registró temperatura mínima En contraste con el calor registrado en la costa, Incahuasi presentó la temperatura mínima más baja del departamento, con 10.4 °C.
+En esta localidad también se reportaron 0.6 milímetros de precipitación, el mayor acumulado entre las estaciones incluidas en el informe.
+En Puchaca, la temperatura máxima llegó a 29 °C y la mínima fue de 21.2 °C, mientras que en Tongorrape se registró una mínima de 22.4 °C.
+La diferencia entre las condiciones térmicas de la costa y las zonas altoandinas evidencia la variabilidad del tiempo en Lambayeque, donde las temperaturas pueden cambiar considerablemente según la ubicación geográfica y la altitud.
+Lluvias ligeras en cuatro estaciones El reporte meteorológico también registró precipitaciones en cuatro estaciones.
+Incahuasi acumuló 0..6 milímetros; Motupe, 0.4 milímetros; Tongorrape, 0.2 milímetros; y Puchaca, una cantidad inferior a un milímetro.
+En las estaciones de Pasabar, Jayanca, Lambayeque, Tinajones, Oyotún, Sipán, Cayaltí, Vista Florida, aeropuerto de Chiclayo y Reque no se registraron precipitaciones durante el periodo evaluado.
+Aunque los acumulados fueron reducidos, estos registros permiten conocer la distribución de las lluvias en el departamento y seguir la evolución de las condiciones meteorológicas.
+Seguimiento de las condiciones climáticas El Senamhi monitorea las temperaturas máximas y mínimas, así como las precipitaciones registradas en las estaciones meteorológicas del país, información que contribuye a evaluar las condiciones del tiempo y apoyar la planificación de las actividades agrícolas, de transporte y de la población.
+En Lambayeque, los registros de Motupe, Cayaltí y Jayanca destacan por sus elevadas temperaturas máximas, mientras que Incahuasi sobresale por sus condiciones más frías y por concentrar el mayor acumulado de lluvia del periodo analizado.
+Más en Andina: ?? 84 puertos permanecen cerrados en el litoral peruano por oleajes anómalos https://t.co/L22enR4XmI https://t.co/FS6yvDUvuN (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-calor-extremo-lambayeque-region-registra-temperaturas-352-°c-ultimas-24-horas-1097104.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tumbes: miembros del Ejército colocan sacos de arena en para proteger casas ante lluvias</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>@agenciaandina ????? ¡El Ejército apoya en la protección de viviendas ante inundaciones! ?????? Nuestras Fuerzas Armadas despliegan acciones para proteger las viviendas del barrio Bellavista ante el riesgo de inundaciones.
+?? Ya se colocaron 750 sacos de arena y se instalarán otros 350.
+Además, se realizan trabajos de limpieza de canales para facilitar la evacuación del agua.
+???? ?? ¿Cómo está la situación en tu zona? #Tumbes #LluviasEnTumbes #EjércitoDelPerú #Inundaciones ? sonido original - Agencia Andina Así lo informó el Ministerio de Defensa que precisó que en las próximas horas se instalarán otros 350 sacos de arena, que se sumarán a los 400 dispuestos anoche.
+Para agilizar estas labores, el Ejército emplea una máquina que permite llenar y coser los sacos, explicó el comandante general de la 1.ª Brigada de Infantería de Tumbes, general Luis César Núñez, quien está a cargo de los trabajos.
+Lea también: Tumbes soportará lluvias de fuerte intensidad de hasta 40 litros por m² desde hoy viernes Además, el Ejército realiza la limpieza de canales de desfogue para agilizar la evacuación de las aguas pluviales hacia el río Tumbes y reducir el riesgo de inundaciones.
+Estas acciones se coordinan con el Ministerio de Defensa y se ejecutan de manera articulada con otras instituciones, entre ellas el Ministerio de Vivienda, Construcción y Saneamiento, el Gobierno Regional de Tumbes, la Municipalidad Provincial y el Indeci.
+Estos trabajos son desarrollados por efectivos del Agrupamiento de Artillería de la 1.ª Brigada de Infantería de Tumbes, quienes participaron en la evacuación de agua empozada en distintas calles de la ciudad, debido a las lluvias presentadas el día anterior.
+Más en Andina: ?? Visita del papa León XIV: ¿qué días serán no laborables en Lambayeque y Cajamarca.
+??https://t.co/2SGgRpkDEp https://t.co/v4LJf9f47D (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-tumbes-miembros-del-ejercito-colocan-sacos-arena-para-proteger-casas-ante-lluvias-1097065.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>León XIV en Cusco: 130,000 fieles recibirán al papa en Sacsayhuamán y la Plaza de Armas</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Las autoridades multisectoriales, organizaciones, instituciones y voluntarios mantuvieron una última reunión ante la llegada de Su Santidad, con el fin de fortalecer un plan de contingencias que garantice la seguridad y el orden del sumo pontífice y los miles de fieles que arribarán.
+Monseñor Israel Condorhuamán Estrada, vocero y administrador de la Basílica Catedral del Cusco, confirmó a la Agencia Andina que Sacsayhuamán, el principal espacio para la recepción del Santo Padre, y la Plaza de Armas albergará en conjunto hasta 130,000 personas.
+Lea también: ¿Por qué el 15 de noviembre será no laborable solo para sector privado en Cusco y Ucayali? La cantidad de personas que llegarán a Cusco será mucho más, pues se estima que las vías, plazas y zonas adyacentes rebasarán de fieles por la llegada de la comunidad católica y feligresía de los departamentos cercanos, el sur del país y otros países del continente.
+Para ser ubicados en los espacios principales el Arzobispado de Cusco alista códigos QR y brazaletes que permita la identificación de los asistentes “hay una institución con la que estamos haciendo un cuerdo, un contrato, para que nos asesore cómo debemos vigilar la identidad de cada persona con su DNI, para que velemos por la seguridad del santo padre”, expresó.
+En Sacsayhuamán, que cuenta con una extensa explanada abrazada de gigantescos megalitos Inca, ingresará la feligresía en general, mientras que en el Hawkaypata o Plaza Mayor estarán personas vulnerables, de la tercera edad, con enfermedades, limitaciones físicas, gestantes, niños.
+Lea también: Cusco tiene todo listo para recibir al papa León XIV, dice coordinador nacional de visita El resto de personas va ver la transmisión en simultáneamente en las Plazas Regocijo y San Francisco donde se instalarán dos pantallas gigantes (en cada una) “el ángelus que el Papa va dirigir se va a transmitir a nivel mundial”, explicó monseñor, pero aún no se reveló el acto litúrgico que se ofrecerá en Sacsayhuamán.
+“Yo calculo que Sacsayhuamán va colapsar.
+Creo que lo ideal sería, además de verlo y tocarlo, escuchar el mensaje, pero muchos hermanos se conforman habiéndolo visto por el tramo desde el aeropuerto a Sacsayhuamán ida y vuelta, porque va volver por el mismo camino que ha venido”, señaló, afirmando que se tendrá que prever.
+La seguridad del papa también estará a cargo de las Fuerzas Armadas y la guardia Suiza del Vaticano.
+Las coordinaciones al respecto ya se desarrollan.
+Más en Andina: ?? Visita del papa León XIV: ¿qué días serán no laborables en Lambayeque y Cajamarca.
+??https://t.co/2SGgRpkDEp https://t.co/v4LJf9f47D (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-leon-xiv-cusco-130000-fieles-recibiran-al-papa-sacsayhuaman-y-plaza-armas-1097071.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Papa León XIV en Lambayeque: artesanas convierten la paja palma macora en recuerdos únicos</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Portarretratos tejidos a mano, llaveros, imanes, pulseras, portarretratos multicolores, accesorios religiosos y artículos utilitarios forman parte de esta novedosa colección que combina identidad cultural, creatividad y fe.
 Cada pieza representa una alternativa para llevarse un recuerdo de la tierra donde Robert Prevost desarrolló parte importante de su labor pastoral antes de convertirse en León XIV.
@@ -775,223 +983,9 @@
 ?? https://t.co/8unyrFk8Uq https://t.co/NO45JnuUnB (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-papa-leon-xiv-lambayeque-artesanas-convierten-paja-palma-macora-recuerdos-unicos-1097075.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Resultados ONPE en región Lambayeque al 99.609 %: aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios iniciaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación en región Lambayeque según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/resultados-en-lambayeque-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Gobierno declara días no laborables por visita del Papa León XIV al Perú</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>La medida, publicada en el boletín Normas Legales del Diario Oficial El Peruano, alcanza a los trabajadores del sector público y privado, de acuerdo con las fechas establecidas para cada ámbito geográfico, tal como se detalla a continuación: Sector público Departamento y fecha declarada no laborable Lima • 11 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 12 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 16 de noviembre de 2026 Provincia Constitucional del Callao • 11 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 12 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 16 de noviembre de 2026 Cajamarca, La Libertad, Lambayeque y Piura • 13 y 14 de noviembre de 2026 Sector privado Departamento y fecha declarada no laborable Lima • 11 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 12 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 16 de noviembre de 2026 Provincia Constitucional del Callao • 11 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 12 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 16 de noviembre de 2026 Cajamarca, La Libertad, Lambayeque y Piura • 13 y 14 de noviembre de 2026 Cusco • 15 de noviembre de 2026 Ucayali • 15 de noviembre de 2026 A diferencia de un feriado, que otorga descanso remunerado sin recuperación de horas, el día no laborable compensable exige recuperar las horas dejadas de trabajar.
-En el sector privado, acogerse a esta medida requiere un acuerdo entre el empleador y los trabajadores; si no lo hay, decide el empleador.
-Lee también Papa León XIV en Perú: helicóptero de la FAP acompañará sus traslados en el norte Visita de trascendencia espiritual, histórica y social El decreto -que lleva las rúbricas de la presidenta Keiko Fujimori; del presidente del Consejo de Ministros, Luis Galarreta; y del titular de Trabajo Juan Sheput- señala que la visita del pontífice, prevista del 11 al 16 de noviembre de 2026, constituye un acontecimiento de especial trascendencia espiritual, histórica y social para el país.
-También indica que la medida busca facilitar la asistencia de las personas a los eventos y reuniones vinculados con la visita.
-¿Como se recuperarán las horas dejadas de trabajar? Respecto a la recuperación de las horas no trabajadas, en el sector público estas deberán compensarse dentro de los 10 días posteriores o en la oportunidad que establezca el titular de cada entidad.
-En el sector privado, el acuerdo entre el empleador y los trabajadores deberá establecer cómo se recuperarán las horas; a falta de consenso, la decisión corresponderá al empleador.
-Lee también Papa León XIV: cardenal de Lima habla sobre itinerario de Sumo Pontífice tras cirugía Servicios indispensables La norma también dispone que las entidades públicas comprendidas en las jurisdicciones señaladas adopten las medidas necesarias para garantizar la continuidad de los servicios públicos indispensables para la comunidad durante los días no laborables.
-Asimismo, las empresas privadas que brindan actividades económicas de especial relevancia para la comunidad podrán determinar los puestos de trabajo excluidos de la medida.
-Esto comprende los servicios sanitarios y de salubridad, limpieza y saneamiento; electricidad, agua, desagüe, gas y combustible; sepelios; comunicaciones y telecomunicaciones; transporte, pesca, puertos, aeropuertos y terrapuertos; establecimientos de hospedaje que reciban y atiendan huéspedes; restaurantes; seguridad, custodia y vigilancia; empresas del sistema financiero y otros servicios financieros; traslado de valores y expendio de víveres y alimentos.
-Más en Andina: ATU realizará feria para informar los beneficios de ampliar carril de bus en Av.
-Arequipa.
-La cita es este domingo 25 y en ella se explicará cómo gestionar el VAPP para acceder a las cocheras.??https://t.co/n2Idy2parG https://t.co/KXDDp86noE (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-gobierno-declara-dias-no-laborables-visita-del-papa-leon-xiv-al-peru-1097045.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Estas son las normas legales más importantes del viernes 23 de octubre de 2026</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Congreso de la República Resolución Legislativa del Senado de la República que elige a tres miembros del directorio del Banco Central de Reserva del Perú .
-Resolución Legislativa 002-2026-2027-S El Senado de la República, en uso de las facultades, ha resuelto elegir a los señores Oswaldo Molina Campodónico, José Ricardo Stok Capella y Juan José Marthans León miembros del directorio del Banco Central de Reserva del Perú.
-Presidencia del Consejo de Ministros Dejan sin efecto la resolución suprema que autorizó viaje de ministro de Desarrollo Agrario y Riego.
-Resolución Suprema 301-2026-PCM Se deja sin efecto la Resolución Suprema 294-2026-PCM, que autorizó el viaje del ministro de Estado en el despacho de Desarrollo Agrario y Riego, Marco Antonio Vinelli Ruiz, a la ciudad de Panamá, República de Panamá, del 21 al 23 de octubre de 2026, para participar en el evento denominado “Diálogo regional de política: construyendo sistemas agroalimentarios productivos y resilientes”.
-Ministerio de Comercio Exterior y Turismo Aprueban el Plan Nacional de Orden Turístico 2026-2031.
-Resolución Ministerial 383-2026-Mincetur Se aprueba el Plan Nacional de Orden Turístico 2026-2031, el cual tiene como objetivo general fortalecer las condiciones para el desarrollo de la actividad turística en los destinos turísticos priorizados, mediante la implementación articulada de acciones sectoriales orientadas a su gestión y desarrollo, seguridad y formalización.
-Su finalidad es contribuir al fortalecimiento de la competitividad de la actividad turística, mediante la generación de condiciones favorables para el desarrollo turístico de dichos destinos.
-Ministerio de Economía y Finanzas Aprueban el instrumento denominado “Estrategia de gestión financiera del riesgo de desastres”.
-Resolución Ministerial 485-2026-EF/52 Se aprueba la “Estrategia de gestión dinanciera del riesgo de desastres”, con la finalidad de fortalecer la capacidad financiera del Estado ante la ocurrencia de desastres.
-Su implementación se financia con cargo al presupuesto institucional de las entidades involucradas, sin demandar recursos adicionales al Tesoro Público.
-Ministerio de Trabajo y Promoción del Empleo Declaran días no laborables compensables por la visita de su santidad el papa León XIV al Perú.
-Decreto Supremo 020-2026-TR El Gobierno declaró días no laborables sujetos a compensación para el sector público y privado en Lima y Callao, Cajamarca, La Libertad, Lambayeque, Piura, Cusco y Ucayali, con motivo de la visita oficial de su santidad el papa León XIV a nuestro país.
-La medida busca facilitar la asistencia y participación de la ciudadanía en los eventos multitudinarios y actividades pastorales programadas durante la estancia del sumo pontífice, declarada previamente de interés nacional.
-Si deseas acceder al boletín Normas Legales haz clic aquí.
-Más en Andina: La presidenta de la república, Keiko Fujimori, destacó la culminación de la excavación de las estaciones de la línea 2 y del ramal de la Línea 4 del Metro de Lima y Callao, como parte de la construcción del primer sistema del metro subterráneo del país.??https://t.co/yukF5fk0Pj https://t.co/7waz0oFpVs (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 22, 2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-estas-son-las-normas-legales-mas-importantes-del-viernes-23-octubre-2026-1097046.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Papa León XIV: con bendición se inició armado de escenario para misa en Pimentel</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>El gobernador de Lambayeque, Jorge Pérez Flores, participó en la ceremonia religiosa encabezada por el párroco de la iglesia Santa María Catedral, Vincent Ventura Valdivia, que congregó a representantes de la Cancillería, la Región Policial Lambayeque, la Municipalidad Distrital de Pimentel y otras autoridades involucradas en la organización.
-La explanada empieza a tomar forma Tras culminar los trabajos de nivelación y acondicionamiento del terreno, ejecutados por el Gobierno Regional de Lambayeque, la Cancillería inició las labores para levantar el escenario donde el santo padre dirigirá su mensaje y celebrará la eucaristía ante una multitud de peregrinos.
-La jornada comenzó con oraciones y una bendición especial para los trabajadores y los profesionales responsables de la construcción.
-El acto simbolizó el inicio de una etapa decisiva para concretar uno de los acontecimientos religiosos más esperados por la población lambayecana.
-En el terreno ya se hacen excavaciones para cimentar las bases de la estructura.
-En paralelo, continúan las coordinaciones técnicas y logísticas para garantizar las condiciones necesarias para el desarrollo de la celebración.
-Cerca de un millón de fieles La magnitud del acontecimiento trasciende las fronteras de Lambayeque.
-La organización proyecta la llegada de cerca de un millón de personas, entre fieles de distintas regiones del Perú y visitantes extranjeros, que buscarán participar en la celebración eucarística del pontífice.
-Para responder a esta movilización multitudinaria se habilitan rutas de acceso y circulación, incluida una vía para proveedores.
-Se proyecta contar con unas ocho rutas, además de medidas especiales para facilitar el traslado de adultos mayores y personas con dificultades de movilidad.
-El acondicionamiento del espacio busca ordenar el desplazamiento de los peregrinos y contribuir a que la jornada se desarrolle en condiciones adecuadas de seguridad y organización.
-Marcará la historia de Lambayeque La visita tiene un significado especial para Chiclayo y toda la región, donde Robert Francis Prevost desarrolló durante años su labor pastoral antes de convertirse en el papa León XIV.
-La expectativa crece entre los ciudadanos que esperan reencontrarse espiritualmente con el pontífice en una tierra que forma parte de su trayectoria religiosa y humana.
-Con el escenario papal en marcha, Lambayeque avanza hacia una jornada de fe, tradición y esperanza.
-Las pampas de Pimentel se preparan para convertirse en el punto de encuentro de miles de peregrinos en una celebración que proyectará la imagen de la región al Perú y al mundo.
-El papa León XIV vuelve a la tierra que marcó su camino pastoral, y Lambayeque se alista para recibirlo con los brazos abiertos.
-Más en Andina: #GaleríaAndina ?? Realizan obras de refaccionamiento de la Catedral de Lima, en el Cercado de Lima, ante la próxima llegada del papa León XIV al Perú.
-Mira la galería completa aquí ?? https://t.co/TdJ2y04nFhFoto: ANDINA/Daniel Bracamonte https://t.co/Buwf6i6LoI (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 24, 2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-papa-leon-xiv-bendicion-se-inicio-armado-escenario-para-misa-pimentel-1097169.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tumbes: miembros del Ejército colocan sacos de arena en para proteger casas ante lluvias</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>@agenciaandina ????? ¡El Ejército apoya en la protección de viviendas ante inundaciones! ?????? Nuestras Fuerzas Armadas despliegan acciones para proteger las viviendas del barrio Bellavista ante el riesgo de inundaciones.
-?? Ya se colocaron 750 sacos de arena y se instalarán otros 350.
-Además, se realizan trabajos de limpieza de canales para facilitar la evacuación del agua.
-???? ?? ¿Cómo está la situación en tu zona? #Tumbes #LluviasEnTumbes #EjércitoDelPerú #Inundaciones ? sonido original - Agencia Andina Así lo informó el Ministerio de Defensa que precisó que en las próximas horas se instalarán otros 350 sacos de arena, que se sumarán a los 400 dispuestos anoche.
-Para agilizar estas labores, el Ejército emplea una máquina que permite llenar y coser los sacos, explicó el comandante general de la 1.ª Brigada de Infantería de Tumbes, general Luis César Núñez, quien está a cargo de los trabajos.
-Lea también: Tumbes soportará lluvias de fuerte intensidad de hasta 40 litros por m² desde hoy viernes Además, el Ejército realiza la limpieza de canales de desfogue para agilizar la evacuación de las aguas pluviales hacia el río Tumbes y reducir el riesgo de inundaciones.
-Estas acciones se coordinan con el Ministerio de Defensa y se ejecutan de manera articulada con otras instituciones, entre ellas el Ministerio de Vivienda, Construcción y Saneamiento, el Gobierno Regional de Tumbes, la Municipalidad Provincial y el Indeci.
-Estos trabajos son desarrollados por efectivos del Agrupamiento de Artillería de la 1.ª Brigada de Infantería de Tumbes, quienes participaron en la evacuación de agua empozada en distintas calles de la ciudad, debido a las lluvias presentadas el día anterior.
-Más en Andina: ?? Visita del papa León XIV: ¿qué días serán no laborables en Lambayeque y Cajamarca.
-??https://t.co/2SGgRpkDEp https://t.co/v4LJf9f47D (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-tumbes-miembros-del-ejercito-colocan-sacos-arena-para-proteger-casas-ante-lluvias-1097065.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Huancavelica: ANA muestra cómo el agua del río Mantaro se transforma en electricidad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>La actividad, desarrollada a través del Consejo de Recursos Hídricos de Cuenca Interregional Mantaro, en coordinación con la Empresa de Electricidad del Perú (Electroperú S.A.), contó con la participación de representantes de los consejos de cuenca de Pasco, Junín, Huancavelica y Ayacucho, y jóvenes de la promoción 2026 de la Red Agua Joven de la Cuenca Mantaro.
-Durante el recorrido, los asistentes conocieron cómo se aprovecha el agua desde su captación en la represa de Tablachaca.
-Desde allí, el recurso es conducido por un túnel de 19.8 kilómetros hasta la central Santiago Antúnez de Mayolo, donde mueve siete turbinas para generar electricidad.
-Después, continúa hacia la hidroeléctrica Restitución, donde impulsa otras tres turbinas y permite aprovechar su energía.
-Los especialistas de Electroperú explicaron los procesos de operación, mantenimiento, monitoreo y seguridad de estas instalaciones.
-La central Santiago Antúnez de Mayolo tiene una potencia efectiva de 890 megavatios (MW) y forma parte del complejo hidroeléctrico Mantaro, que contribuye al abastecimiento del Sistema Eléctrico Interconectado Nacional (SEIN).
-Electricidad y agua La delegación estuvo integrada por representantes de gobiernos regionales y locales, comunidades campesinas, organizaciones de usuarios de agua, empresas prestadoras de servicios de saneamiento, colegios profesionales y universidades.
-El intercambio permitió conocer más sobre la relación entre la generación de electricidad y las necesidades de los diferentes sectores que utilizan el agua en la cuenca.
-Además, los jóvenes universitarios del programa de voluntariado de la ANA, a cargo de la Autoridad Administrativa del Agua (AAA) Mantaro, conocieron las instalaciones de la subestación del campamento de Campo Armiño.
-La visita forma parte de las actividades por el Mes del Río Mantaro.
-A través de estas iniciativas, la ANA promueve el conocimiento sobre los diferentes usos del agua y su importancia para la generación de energía eléctrica, así como el intercambio de experiencias entre los actores que participan en la gestión de los recursos hídricos de la cuenca.
-Más en Andina: El distrito de Reque, en Lambayeque, se alista para celebrar la tradicional fiesta patronal en honor a san Martín de Thours.
-Esta festividad coincidirá con la visita del papa León XIV.
-https://t.co/WMZjJwyYvz https://t.co/kwbsAjW86j (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-huancavelica-ana-muestra-como-agua-del-rio-mantaro-se-transforma-electricidad-1097152.aspx</t>
         </is>
       </c>
     </row>
@@ -1006,158 +1000,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>León XIV en Cusco: 130,000 fieles recibirán al papa en Sacsayhuamán y la Plaza de Armas</t>
+          <t>Escenario de sequía prolongada obliga a reforzar los equipos ante incendios forestales</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>Las autoridades multisectoriales, organizaciones, instituciones y voluntarios mantuvieron una última reunión ante la llegada de Su Santidad, con el fin de fortalecer un plan de contingencias que garantice la seguridad y el orden del sumo pontífice y los miles de fieles que arribarán.
-Monseñor Israel Condorhuamán Estrada, vocero y administrador de la Basílica Catedral del Cusco, confirmó a la Agencia Andina que Sacsayhuamán, el principal espacio para la recepción del Santo Padre, y la Plaza de Armas albergará en conjunto hasta 130,000 personas.
-Lea también: ¿Por qué el 15 de noviembre será no laborable solo para sector privado en Cusco y Ucayali? La cantidad de personas que llegarán a Cusco será mucho más, pues se estima que las vías, plazas y zonas adyacentes rebasarán de fieles por la llegada de la comunidad católica y feligresía de los departamentos cercanos, el sur del país y otros países del continente.
-Para ser ubicados en los espacios principales el Arzobispado de Cusco alista códigos QR y brazaletes que permita la identificación de los asistentes “hay una institución con la que estamos haciendo un cuerdo, un contrato, para que nos asesore cómo debemos vigilar la identidad de cada persona con su DNI, para que velemos por la seguridad del santo padre”, expresó.
-En Sacsayhuamán, que cuenta con una extensa explanada abrazada de gigantescos megalitos Inca, ingresará la feligresía en general, mientras que en el Hawkaypata o Plaza Mayor estarán personas vulnerables, de la tercera edad, con enfermedades, limitaciones físicas, gestantes, niños.
-Lea también: Cusco tiene todo listo para recibir al papa León XIV, dice coordinador nacional de visita El resto de personas va ver la transmisión en simultáneamente en las Plazas Regocijo y San Francisco donde se instalarán dos pantallas gigantes (en cada una) “el ángelus que el Papa va dirigir se va a transmitir a nivel mundial”, explicó monseñor, pero aún no se reveló el acto litúrgico que se ofrecerá en Sacsayhuamán.
-“Yo calculo que Sacsayhuamán va colapsar.
-Creo que lo ideal sería, además de verlo y tocarlo, escuchar el mensaje, pero muchos hermanos se conforman habiéndolo visto por el tramo desde el aeropuerto a Sacsayhuamán ida y vuelta, porque va volver por el mismo camino que ha venido”, señaló, afirmando que se tendrá que prever.
-La seguridad del papa también estará a cargo de las Fuerzas Armadas y la guardia Suiza del Vaticano.
-Las coordinaciones al respecto ya se desarrollan.
-Más en Andina: ?? Visita del papa León XIV: ¿qué días serán no laborables en Lambayeque y Cajamarca.
-??https://t.co/2SGgRpkDEp https://t.co/v4LJf9f47D (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-leon-xiv-cusco-130000-fieles-recibiran-al-papa-sacsayhuaman-y-plaza-armas-1097071.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Senamhi: decimotercer friaje ingresará desde la noche del domingo 25 de octubre</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Esta masa de aire frío ingresará al territorio nacional por la selva sur (departamentos de Puno, Madre de Dios y Cusco) y se desplazará hacia la selva central.
-Durante su desarrollo se presentará el descenso de las temperaturas, lluvias con descargas eléctricas, ráfagas de viento con velocidades alrededor de los 50 kilómetrospor hora (km/h) y cobertura nubosa.
-Durante este período, las temperaturas nocturnas (mínimas) alcanzarían valores próximos a 19 °C en la selva sur, y entre 18.0 °C y 21.0 °C en la selva central, detalló el organismo adscrito al Ministerio del Ambiente (Minam).
-Asimismo, las temperaturas diurnas (máximas) bordearán los 29 °C en la selva sur y alrededor de los 27.0 °C en la selva central.
-El Minam, a través del Senamhi, continuará emitiendo información actualizada sobre el comportamiento del tiempo y clima y recomienda a la población mantenerse informada a través de la página web y redes sociales.
-Más en Andina: El distrito de Reque, en Lambayeque, se alista para celebrar la tradicional fiesta patronal en honor a san Martín de Thours.
-Esta festividad coincidirá con la visita del papa León XIV.
-https://t.co/WMZjJwyYvz https://t.co/kwbsAjW86j (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-senamhi-decimotercer-friaje-ingresara-desde-noche-del-domingo-25-octubre-1097162.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Minedu expone acciones ante violencia escolar y de prevención por El Niño en Lambayeque</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>El viceministro de Gestión Institucional, Luis Antonio Aleman Nakamine, participó en representación del ministro de Educación, José Antonio Chang Escobedo, en la primera audiencia pública descentralizada “Diálogo en Lambayeque: avances y resultados en educación, cultura y deporte”, organizada por la Comisión de Educación, Cultura y Deporte de la Cámara de Diputados.
-Aleman Nakamine expuso las acciones implementadas por el sector frente a los casos de violencia escolar y los nuevos lineamientos de gestión escolar, orientados a regular el comportamiento de los estudiantes, promover una convivencia respetuosa y reforzar la autoridad docente.
-Participaron representantes de la Gerencia Regional de Educación, las UGEL, el Ministerio Público, organizaciones de padres de familia y otros actores de la comunidad.
-Trabajo articulado “Tenemos que trabajar unidos y de manera articulada para recuperar el orden y la disciplina en nuestras escuelas, garantizar ambientes seguros para los estudiantes y restablecer el respeto en los colegios.
-Estamos a tiempo de hacerlo si sumamos esfuerzos entre las autoridades educativas, los docentes y las familias” , precisó.
-La actividad se desarrolló en la sede de la Unidad de Gestión Educativa Local (UGEL) Chiclayo, con la participación de docentes, funcionarios del Gobierno Regional de Lambayeque y representantes de diversas instituciones, quienes dialogaron sobre los avances y desafíos del sector en la región.
-Durante la audiencia se abordaron dos temas prioritarios para el Minedu: las acciones preventivas y de contingencia para proteger la infraestructura educativa frente a los posibles efectos del fenómeno El Niño (FEN), y las medidas adoptadas ante los casos de violencia escolar reportados durante 2026 en la plataforma SíseVe.
-Infraestructura En materia de infraestructura, el Programa Nacional de Infraestructura Educativa (Pronied) informó sobre los avances del plan de contingencia, las obras de prevención y las acciones de reconstrucción en locales escolares vulnerables frente a lluvias intensas e inundaciones.
-Estas intervenciones buscan reducir los riesgos y contribuir a la continuidad del servicio educativo ante posibles emergencias.
-La participación del Minedu en este espacio de diálogo permitió informar sobre las medidas del sector y recoger consultas y aportes de los participantes, con énfasis en la prevención de riesgos, la protección de los estudiantes y la respuesta oportuna ante situaciones que afectan la convivencia escolar.
-Más en Andina: El distrito de Reque, en Lambayeque, se alista para celebrar la tradicional fiesta patronal en honor a san Martín de Thours.
-Esta festividad coincidirá con la visita del papa León XIV.
-https://t.co/WMZjJwyYvz https://t.co/kwbsAjW86j (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-minedu-expone-acciones-ante-violencia-escolar-y-prevencion-por-nino-lambayeque-1097160.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Calor extremo en Lambayeque: región registra temperaturas de 35.2 °C en últimas 24 horas</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>El informe, que comprende el periodo desde las 7:00 a.
-m.
-del jueves 22 hasta las 7:00 a.
-m.
-del viernes 23 de octubre, revela que las localidades de la costa lambayecana continúan registrando temperaturas elevadas , mientras que en las zonas altoandinas se presentan condiciones más frías, como en Incahuasi, donde la temperatura mínima descendió a 10.4 °C.
-Motupe y Cayaltí encabezaron los registros de temperatura máxima , con 35.2 °C cada una , seguidas de Jayanca, con 35 °C; Sipán y Vista Florida, en Chiclayo, con 34.9 °C; y Oyotún, con 33.6 °C.
-En Pasabar, distrito de Olmos, se reportaron 33.4 °C.
-Otros registros fueron 33.2 °C en Lambayeque, 32.7 °C en el aeropuerto de Chiclayo, 32.6 °C en Tongorrape y Tinajones, y 30.6 °C en Reque.
-Incahuasi registró temperatura mínima En contraste con el calor registrado en la costa, Incahuasi presentó la temperatura mínima más baja del departamento, con 10.4 °C.
-En esta localidad también se reportaron 0.6 milímetros de precipitación, el mayor acumulado entre las estaciones incluidas en el informe.
-En Puchaca, la temperatura máxima llegó a 29 °C y la mínima fue de 21.2 °C, mientras que en Tongorrape se registró una mínima de 22.4 °C.
-La diferencia entre las condiciones térmicas de la costa y las zonas altoandinas evidencia la variabilidad del tiempo en Lambayeque, donde las temperaturas pueden cambiar considerablemente según la ubicación geográfica y la altitud.
-Lluvias ligeras en cuatro estaciones El reporte meteorológico también registró precipitaciones en cuatro estaciones.
-Incahuasi acumuló 0..6 milímetros; Motupe, 0.4 milímetros; Tongorrape, 0.2 milímetros; y Puchaca, una cantidad inferior a un milímetro.
-En las estaciones de Pasabar, Jayanca, Lambayeque, Tinajones, Oyotún, Sipán, Cayaltí, Vista Florida, aeropuerto de Chiclayo y Reque no se registraron precipitaciones durante el periodo evaluado.
-Aunque los acumulados fueron reducidos, estos registros permiten conocer la distribución de las lluvias en el departamento y seguir la evolución de las condiciones meteorológicas.
-Seguimiento de las condiciones climáticas El Senamhi monitorea las temperaturas máximas y mínimas, así como las precipitaciones registradas en las estaciones meteorológicas del país, información que contribuye a evaluar las condiciones del tiempo y apoyar la planificación de las actividades agrícolas, de transporte y de la población.
-En Lambayeque, los registros de Motupe, Cayaltí y Jayanca destacan por sus elevadas temperaturas máximas, mientras que Incahuasi sobresale por sus condiciones más frías y por concentrar el mayor acumulado de lluvia del periodo analizado.
-Más en Andina: ?? 84 puertos permanecen cerrados en el litoral peruano por oleajes anómalos https://t.co/L22enR4XmI https://t.co/FS6yvDUvuN (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-calor-extremo-lambayeque-region-registra-temperaturas-352-°c-ultimas-24-horas-1097104.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Escenario de sequía prolongada obliga a reforzar los equipos ante incendios forestales</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
         <is>
           <t>Tras su participación en la feria ExpoAmazónica 2026 que se celebra en Pucallpa, el ministro Vinelli afirmóque el país debe prepararse para un escenario de sequía prolongada que podría favorecer la propagación de incendios, por lo que se prevé incrementar los equipos destinados a las labores de extinción y fortalecer la participación del personal de las Fuerzas Armadas.
 “Estamos preparándonos para lo que se viene con el fenómeno de El Niño”, manifestó durante una entrevista en el marco de la Expo Amazónica 2026, en Pucallpa.
@@ -1184,27 +1030,27 @@
 Más en Andina: ¡Calor extremo en Lambayeque! ?? La región registra temperaturas de 35.2 °C en últimas 24 horas https://t.co/XskagCqsy8 https://t.co/fOAi0z937y (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-escenario-sequia-prolongada-obliga-a-reforzar-los-equipos-ante-incendios-forestales-1097109.aspx</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Reniec atenderá hoy sábado 24 de octubre en más de 100 sedes a nivel nacional</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>El horario de atención en dichas sedes habilitadas es diferenciado.
 Por ese motivo, la institución insta a los ciudadanos a revisar la lista de oficinas y horarios antes de acudir a una de estas.
@@ -1229,27 +1075,27 @@
 Más en Andina: ??Conoce el horario de ingreso, documentos a llevar y objetos prohibidos en el examen de admisión UNMSM 2027-I https://t.co/5ER16JNGrc https://t.co/NB1gltZIet (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-reniec-atendera-hoy-sabado-24-octubre-mas-100-sedes-a-nivel-nacional-1097137.aspx</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Reque se viste de fe: fiesta patronal de san Martín de Thours coincidirá con visita papal</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>La noticia de la evolución de la salud del santo padre ha renovado el entusiasmo de los fieles lambayecanos, que mantienen viva la esperanza de recibir a Robert Prevost en la tierra donde dejó una profunda huella pastoral durante sus años como obispo de Chiclayo.
 En este ambiente de esperanza, Reque también se prepara para convertirse en uno de los puntos de encuentro de la fe, la identidad y las tradiciones de Lambayeque.
@@ -1278,27 +1124,27 @@
 ?? https://t.co/axgDDtLaVs (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-reque-se-viste-fe-fiesta-patronal-san-martin-thours-coincidira-visita-papal-1097143.aspx</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Comisión de Infraestructura: Sunass expone resultados de supervisión en la costa norte</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>En la sesión, presidida por el diputado Luis Quispe Candia (Buen Gobierno), la comisión recibió al gerente general de la Superintendencia Nacional de Servicios de Saneamiento (Sunass), Manuel Muñoz Quiroz, quien expuso los resultados de las labores de supervisión en Tumbes, Piura, Lambayeque, La Libertad y Áncash.
 El representante de la Sunass informó que, de un total de 135 infraestructuras evaluadas –entre captaciones, pozos, reservorios y estaciones de bombeo–, 101 presentan vulnerabilidades con riesgo crítico.
@@ -1310,34 +1156,193 @@
 ?? https://t.co/OfhzcJn6JV (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-comision-infraestructura-sunass-expone-resultados-supervision-la-costa-norte-1097149.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Huancavelica: ANA muestra cómo el agua del río Mantaro se transforma en electricidad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>La actividad, desarrollada a través del Consejo de Recursos Hídricos de Cuenca Interregional Mantaro, en coordinación con la Empresa de Electricidad del Perú (Electroperú S.A.), contó con la participación de representantes de los consejos de cuenca de Pasco, Junín, Huancavelica y Ayacucho, y jóvenes de la promoción 2026 de la Red Agua Joven de la Cuenca Mantaro.
+Durante el recorrido, los asistentes conocieron cómo se aprovecha el agua desde su captación en la represa de Tablachaca.
+Desde allí, el recurso es conducido por un túnel de 19.8 kilómetros hasta la central Santiago Antúnez de Mayolo, donde mueve siete turbinas para generar electricidad.
+Después, continúa hacia la hidroeléctrica Restitución, donde impulsa otras tres turbinas y permite aprovechar su energía.
+Los especialistas de Electroperú explicaron los procesos de operación, mantenimiento, monitoreo y seguridad de estas instalaciones.
+La central Santiago Antúnez de Mayolo tiene una potencia efectiva de 890 megavatios (MW) y forma parte del complejo hidroeléctrico Mantaro, que contribuye al abastecimiento del Sistema Eléctrico Interconectado Nacional (SEIN).
+Electricidad y agua La delegación estuvo integrada por representantes de gobiernos regionales y locales, comunidades campesinas, organizaciones de usuarios de agua, empresas prestadoras de servicios de saneamiento, colegios profesionales y universidades.
+El intercambio permitió conocer más sobre la relación entre la generación de electricidad y las necesidades de los diferentes sectores que utilizan el agua en la cuenca.
+Además, los jóvenes universitarios del programa de voluntariado de la ANA, a cargo de la Autoridad Administrativa del Agua (AAA) Mantaro, conocieron las instalaciones de la subestación del campamento de Campo Armiño.
+La visita forma parte de las actividades por el Mes del Río Mantaro.
+A través de estas iniciativas, la ANA promueve el conocimiento sobre los diferentes usos del agua y su importancia para la generación de energía eléctrica, así como el intercambio de experiencias entre los actores que participan en la gestión de los recursos hídricos de la cuenca.
+Más en Andina: El distrito de Reque, en Lambayeque, se alista para celebrar la tradicional fiesta patronal en honor a san Martín de Thours.
+Esta festividad coincidirá con la visita del papa León XIV.
+https://t.co/WMZjJwyYvz https://t.co/kwbsAjW86j (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-huancavelica-ana-muestra-como-agua-del-rio-mantaro-se-transforma-electricidad-1097152.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Visita del papa León XIV: Perú ofrece 220,000 plazas-cama en destinos de su recorrido</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MEF señala que están trabajando para que economía crezca sostenidamente en próximos 5 años Según la información del sector, esta capacidad de alojamiento comprende alrededor de 126,000 habitaciones disponibles.
+Además, se suman unas 48,000 habitaciones de alquiler temporal a través de plataformas como Airbnb, que amplían las alternativas para los visitantes nacionales y extranjeros.
+Lima y Callao concentran la mayor oferta, con 167,000 plazas-cama en aproximadamente 9,000 establecimientos de hospedaje.
+Les siguen Cusco, con 28,000 plazas-cama en cerca de 1,100 establecimientos; Chiclayo y localidades cercanas de las provincias de Lambayeque y Ferreñafe, con 15,000 plazas-cama en 569 establecimientos; Pucallpa, con 9,000 plazas-cama; y Santa Cruz de Succhabamba y Chota, en Cajamarca, con 2,000 plazas-cama.
+Las cifras corresponden a junio de 2026 y dan cuenta de la capacidad de alojamiento registrada en los ámbitos considerados para la visita papal.
+Impacto en la economía El Mincetur proyecta que la visita del papa León XIV podría atraer a más de 854,000 visitantes a los destinos incluidos en su itinerario y generar un impacto económico directo estimado en 308,4 millones de soles.
+La llegada de viajeros representa una oportunidad para dinamizar las economías locales mediante una mayor demanda de servicios turísticos, entre ellos hospedaje, alimentación, transporte y comercio, con efectos en los ingresos de emprendedores y trabajadores de las localidades anfitrionas.
+A nivel nacional, el Perú registró 28,722 establecimientos de hospedaje en 2025, de acuerdo con el informe anual del Mincetur.
+Esta cifra representó un crecimiento de 2,4% respecto al año anterior y superó en 20,1% los niveles prepandemia, según el sector.
+Más en Andina: ?? Las ventas de vehículos livianos nuevos alcanzaron un pico histórico entre enero y agosto del 2026, al sumar 167,244 unidades comercializadas, cifra que representa un crecimiento de 39.5%.
+https://t.co/CnOVIriRwF pic.twitter.com/umjYiIKhwh (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) September 18, 2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-visita-del-papa-leon-xiv-peru-ofrece-220000-plazascama-destinos-su-recorrido-1097155.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Minedu expone acciones ante violencia escolar y de prevención por El Niño en Lambayeque</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>El viceministro de Gestión Institucional, Luis Antonio Aleman Nakamine, participó en representación del ministro de Educación, José Antonio Chang Escobedo, en la primera audiencia pública descentralizada “Diálogo en Lambayeque: avances y resultados en educación, cultura y deporte”, organizada por la Comisión de Educación, Cultura y Deporte de la Cámara de Diputados.
+Aleman Nakamine expuso las acciones implementadas por el sector frente a los casos de violencia escolar y los nuevos lineamientos de gestión escolar, orientados a regular el comportamiento de los estudiantes, promover una convivencia respetuosa y reforzar la autoridad docente.
+Participaron representantes de la Gerencia Regional de Educación, las UGEL, el Ministerio Público, organizaciones de padres de familia y otros actores de la comunidad.
+Trabajo articulado “Tenemos que trabajar unidos y de manera articulada para recuperar el orden y la disciplina en nuestras escuelas, garantizar ambientes seguros para los estudiantes y restablecer el respeto en los colegios.
+Estamos a tiempo de hacerlo si sumamos esfuerzos entre las autoridades educativas, los docentes y las familias” , precisó.
+La actividad se desarrolló en la sede de la Unidad de Gestión Educativa Local (UGEL) Chiclayo, con la participación de docentes, funcionarios del Gobierno Regional de Lambayeque y representantes de diversas instituciones, quienes dialogaron sobre los avances y desafíos del sector en la región.
+Durante la audiencia se abordaron dos temas prioritarios para el Minedu: las acciones preventivas y de contingencia para proteger la infraestructura educativa frente a los posibles efectos del fenómeno El Niño (FEN), y las medidas adoptadas ante los casos de violencia escolar reportados durante 2026 en la plataforma SíseVe.
+Infraestructura En materia de infraestructura, el Programa Nacional de Infraestructura Educativa (Pronied) informó sobre los avances del plan de contingencia, las obras de prevención y las acciones de reconstrucción en locales escolares vulnerables frente a lluvias intensas e inundaciones.
+Estas intervenciones buscan reducir los riesgos y contribuir a la continuidad del servicio educativo ante posibles emergencias.
+La participación del Minedu en este espacio de diálogo permitió informar sobre las medidas del sector y recoger consultas y aportes de los participantes, con énfasis en la prevención de riesgos, la protección de los estudiantes y la respuesta oportuna ante situaciones que afectan la convivencia escolar.
+Más en Andina: El distrito de Reque, en Lambayeque, se alista para celebrar la tradicional fiesta patronal en honor a san Martín de Thours.
+Esta festividad coincidirá con la visita del papa León XIV.
+https://t.co/WMZjJwyYvz https://t.co/kwbsAjW86j (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-minedu-expone-acciones-ante-violencia-escolar-y-prevencion-por-nino-lambayeque-1097160.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Senamhi: decimotercer friaje ingresará desde la noche del domingo 25 de octubre</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Esta masa de aire frío ingresará al territorio nacional por la selva sur (departamentos de Puno, Madre de Dios y Cusco) y se desplazará hacia la selva central.
+Durante su desarrollo se presentará el descenso de las temperaturas, lluvias con descargas eléctricas, ráfagas de viento con velocidades alrededor de los 50 kilómetrospor hora (km/h) y cobertura nubosa.
+Durante este período, las temperaturas nocturnas (mínimas) alcanzarían valores próximos a 19 °C en la selva sur, y entre 18.0 °C y 21.0 °C en la selva central, detalló el organismo adscrito al Ministerio del Ambiente (Minam).
+Asimismo, las temperaturas diurnas (máximas) bordearán los 29 °C en la selva sur y alrededor de los 27.0 °C en la selva central.
+El Minam, a través del Senamhi, continuará emitiendo información actualizada sobre el comportamiento del tiempo y clima y recomienda a la población mantenerse informada a través de la página web y redes sociales.
+Más en Andina: El distrito de Reque, en Lambayeque, se alista para celebrar la tradicional fiesta patronal en honor a san Martín de Thours.
+Esta festividad coincidirá con la visita del papa León XIV.
+https://t.co/WMZjJwyYvz https://t.co/kwbsAjW86j (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-comision-infraestructura-sunass-expone-resultados-supervision-la-costa-norte-1097149.aspx</t>
+          <t>https://andina.pe/agencia/noticia-senamhi-decimotercer-friaje-ingresara-desde-noche-del-domingo-25-octubre-1097162.aspx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Chiclayo (Lambayeque)</t>
+          <t>Papa León XIV: con bendición se inició armado de escenario para misa en Pimentel</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Chiclayo, según el conteo oficial de la ONPE al 98.573% , arroja el siguiente resultado (actualizado el 19/10/2026, a las 08:20.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>El gobernador de Lambayeque, Jorge Pérez Flores, participó en la ceremonia religiosa encabezada por el párroco de la iglesia Santa María Catedral, Vincent Ventura Valdivia, que congregó a representantes de la Cancillería, la Región Policial Lambayeque, la Municipalidad Distrital de Pimentel y otras autoridades involucradas en la organización.
+La explanada empieza a tomar forma Tras culminar los trabajos de nivelación y acondicionamiento del terreno, ejecutados por el Gobierno Regional de Lambayeque, la Cancillería inició las labores para levantar el escenario donde el santo padre dirigirá su mensaje y celebrará la eucaristía ante una multitud de peregrinos.
+La jornada comenzó con oraciones y una bendición especial para los trabajadores y los profesionales responsables de la construcción.
+El acto simbolizó el inicio de una etapa decisiva para concretar uno de los acontecimientos religiosos más esperados por la población lambayecana.
+En el terreno ya se hacen excavaciones para cimentar las bases de la estructura.
+En paralelo, continúan las coordinaciones técnicas y logísticas para garantizar las condiciones necesarias para el desarrollo de la celebración.
+Cerca de un millón de fieles La magnitud del acontecimiento trasciende las fronteras de Lambayeque.
+La organización proyecta la llegada de cerca de un millón de personas, entre fieles de distintas regiones del Perú y visitantes extranjeros, que buscarán participar en la celebración eucarística del pontífice.
+Para responder a esta movilización multitudinaria se habilitan rutas de acceso y circulación, incluida una vía para proveedores.
+Se proyecta contar con unas ocho rutas, además de medidas especiales para facilitar el traslado de adultos mayores y personas con dificultades de movilidad.
+El acondicionamiento del espacio busca ordenar el desplazamiento de los peregrinos y contribuir a que la jornada se desarrolle en condiciones adecuadas de seguridad y organización.
+Marcará la historia de Lambayeque La visita tiene un significado especial para Chiclayo y toda la región, donde Robert Francis Prevost desarrolló durante años su labor pastoral antes de convertirse en el papa León XIV.
+La expectativa crece entre los ciudadanos que esperan reencontrarse espiritualmente con el pontífice en una tierra que forma parte de su trayectoria religiosa y humana.
+Con el escenario papal en marcha, Lambayeque avanza hacia una jornada de fe, tradición y esperanza.
+Las pampas de Pimentel se preparan para convertirse en el punto de encuentro de miles de peregrinos en una celebración que proyectará la imagen de la región al Perú y al mundo.
+El papa León XIV vuelve a la tierra que marcó su camino pastoral, y Lambayeque se alista para recibirlo con los brazos abiertos.
+Más en Andina: #GaleríaAndina ?? Realizan obras de refaccionamiento de la Catedral de Lima, en el Cercado de Lima, ante la próxima llegada del papa León XIV al Perú.
+Mira la galería completa aquí ?? https://t.co/TdJ2y04nFhFoto: ANDINA/Daniel Bracamonte https://t.co/Buwf6i6LoI (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 24, 2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-chiclayo-lambayeque-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-papa-leon-xiv-bendicion-se-inicio-armado-escenario-para-misa-pimentel-1097169.aspx</t>
         </is>
       </c>
     </row>
@@ -1377,15 +1382,40 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Chiclayo (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Chiclayo, según el conteo oficial de la ONPE al 98.573% , arroja el siguiente resultado (actualizado el 19/10/2026, a las 08:20.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-chiclayo-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Lambayeque</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 99.47% , arroja el siguiente resultado (actualizado el 19/10/2026, a las 08:15.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-lambayeque-noticia/</t>
         </is>
